--- a/Supplementary_Materials/TableS8_Results.xlsx
+++ b/Supplementary_Materials/TableS8_Results.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sunnan/Documents/当前在研的所有项目/项目1-1-转录组数据分类/scMFF/手稿/Supplementary Materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sunnan/Documents/当前在研的所有项目/项目1-1-转录组数据分类/scMFF/手稿/Supplementary_Materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A2768E-B725-7E40-BB50-0E6A3E15E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C662130-55A2-8D49-A6B7-904A448526BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="25600" windowHeight="14260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exp1_SingleFeature_Performance" sheetId="3" r:id="rId1"/>
     <sheet name="Exp2_FusionFeature_Performance" sheetId="4" r:id="rId2"/>
-    <sheet name="Exp3_Classifier_Performance" sheetId="5" r:id="rId3"/>
-    <sheet name="Exp4_Ablation_Study" sheetId="6" r:id="rId4"/>
+    <sheet name="Classifier_Performance" sheetId="5" r:id="rId3"/>
+    <sheet name="Exp3_Ablation_Study" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
